--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260706.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260706.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.89%</t>
+          <t>10.33%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>4,486,000</t>
+          <t>25,098,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.22%</t>
+          <t>8.86%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>25,098,000</t>
+          <t>4,486,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.62%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.14%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2,382,000</t>
+          <t>6,334,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>5.88%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,334,000</t>
+          <t>2,382,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.73%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>5.04%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.98%</t>
+          <t>4.89%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.87%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,949,000</t>
+          <t>5,052,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,052,000</t>
+          <t>8,949,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,160,000</t>
+          <t>12,742,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12,742,000</t>
+          <t>5,160,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -990,46 +990,46 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,811,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>1,811,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>411,000</t>
+          <t>6,275,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>6,275,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>411,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>530,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>12,552,541,768</t>
+          <t>12,101,152,848</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,766,455,179</t>
+          <t>2,308,515,359</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
